--- a/TestCases/My_Appointment_TestCase.xlsx
+++ b/TestCases/My_Appointment_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA4AD8A-4510-4DEA-9378-5E96487C88BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB240A20-BFA2-4FCD-BDE6-9C544EFE289F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,10 +194,10 @@
 Không phát sinh thêm bản ghi lịch hẹn trùng.</t>
   </si>
   <si>
-    <t>TCMyAppointment4_1, TCMyAppointment4_2, TCMyAppointment4_2, TCMyAppointment4_4</t>
+    <t>TCMyAppointment4_1, TCMyAppointment4_2, TCMyAppointment4_3, TCMyAppointment4_4</t>
   </si>
   <si>
-    <t>Lịch hẹn sau khi Admin xác nhận được hiển thị đúng phía Doctor và Doctor có thể mở chức năng khám cho lịch hẹn tương ứng.</t>
+    <t>Lịch hẹn được cập nhật đúng xuyên suốt từ “Chờ xác nhận” -&gt; “Đã xác nhận” -&gt; “Đã hoàn thành” sau khi Doctor hoàn tất khám.</t>
   </si>
   <si>
     <t>4. Kiểm tra khung giờ được giải phóng sau khi lịch hẹn bị hủy</t>
@@ -224,7 +224,7 @@
 Lịch mới có ID khác và trạng thái “Chờ xác nhận”.</t>
   </si>
   <si>
-    <t>TCMyAppointment5_1, TCMyAppointment5_2, TCMyAppointment5_2</t>
+    <t>TCMyAppointment5_1, TCMyAppointment5_2, TCMyAppointment5_3</t>
   </si>
   <si>
     <t>Lịch hẹn đã hủy không còn chiếm khung giờ, hệ thống cho phép tạo lịch mới tại cùng ngày giờ với trạng thái “Chờ xác nhận”.</t>
@@ -29368,21 +29368,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D18:F18"/>
     <mergeCell ref="D9:F10"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A19:J19"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:J14"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>

--- a/TestCases/My_Appointment_TestCase.xlsx
+++ b/TestCases/My_Appointment_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB240A20-BFA2-4FCD-BDE6-9C544EFE289F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BEB603-8FA1-4DF1-9381-EAB8A9E3414A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MYAPPOINTMENT" sheetId="9" r:id="rId1"/>
+    <sheet name="MYAPPOINTMENT" sheetId="10" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -34,19 +34,19 @@
     <t>SpringMediCareWeb</t>
   </si>
   <si>
-    <t>Module Code：</t>
+    <t>Pass</t>
   </si>
   <si>
-    <t>Test requirement:</t>
-  </si>
-  <si>
-    <t>Pass</t>
+    <t>Fail</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>Module Code：</t>
+  </si>
+  <si>
+    <t>Test requirement:</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -76,10 +76,10 @@
     <t>Note</t>
   </si>
   <si>
-    <t>PATIENT300 - Patient Appointment</t>
+    <t>PATIENT - My Appointments</t>
   </si>
   <si>
-    <t>PATIENT3 - My Appointments</t>
+    <t>Patient Appointment Tracking</t>
   </si>
   <si>
     <t>1. Kiểm tra truy cập trang Lịch hẹn của tôi</t>
@@ -91,10 +91,14 @@
     <t>Kiểm tra lịch hẹn sau khi bệnh nhân đặt thành công được hiển thị trong trang Lịch hẹn của tôi với trạng thái ban đầu là Chờ xác nhận.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ.
-2: Ghi nhận bác sĩ, ngày giờ khám và ghi chú đã nhập.
-3: Mở trang Lịch hẹn của tôi.
-4: Tìm lịch hẹn vừa tạo.</t>
+    <t>1: Đăng nhập bằng tài khoản Patient.
+2: Thực hiện đặt một lịch khám hợp lệ với Doctor và nhập ghi chú.
+3: Xác nhận hệ thống đặt lịch thành công.
+4: Ghi nhận Doctor, ngày giờ khám và ghi chú của lịch vừa tạo.
+5: Mở trang Lịch hẹn của tôi.
+6: Tìm lịch hẹn vừa tạo trong danh sách.
+7: Kiểm tra Doctor, ngày giờ khám và ghi chú hiển thị đúng.
+8: Kiểm tra trạng thái lịch hẹn là “Chờ xác nhận”.</t>
   </si>
   <si>
     <t>Lịch hẹn vừa tạo xuất hiện trong danh sách.
@@ -117,15 +121,14 @@
     <t>Kiểm tra trạng thái lịch hẹn của Patient được cập nhật sau khi Admin xác nhận lịch.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ.
-2: Đăng nhập bằng tài khoản Admin.
-3: Mở chức năng quản lý lịch hẹn.
-4: Tìm lịch hẹn đang ở trạng thái Chờ xác nhận.
-5: Thực hiện Xác nhận lịch hẹn.
-6: Đăng xuất Admin.
-7: Đăng nhập lại bằng Patient sở hữu lịch hẹn.
-8: Mở trang Lịch hẹn của tôi.
-9: Kiểm tra lịch hẹn vừa được Admin xử lý.</t>
+    <t>1: Patient thực hiện đặt một lịch khám hợp lệ và ghi nhận thông tin lịch vừa tạo.
+2: Đăng nhập bằng tài khoản Admin và mở trang Quản lý lịch hẹn.
+3: Tìm đúng lịch hẹn vừa được Patient tạo đang ở trạng thái “Chờ xác nhận”.
+4: Admin thực hiện Xác nhận lịch hẹn.
+5: Kiểm tra lịch hẹn được cập nhật thành “Đã xác nhận” trên trang Admin.
+6: Đăng nhập lại bằng Patient sở hữu lịch hẹn.
+7: Mở trang Lịch hẹn của tôi và tìm lịch vừa được Admin xử lý.
+8: Kiểm tra thông tin lịch hẹn không thay đổi và trạng thái là “Đã xác nhận”.</t>
   </si>
   <si>
     <t>Lịch hẹn vẫn hiển thị đúng bác sĩ, thời gian và ghi chú ban đầu.
@@ -144,15 +147,14 @@
     <t>Kiểm tra trạng thái lịch hẹn của Patient sau khi Admin thực hiện hủy lịch.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ.
-2: Đăng nhập bằng tài khoản Admin.
-3: Mở chức năng Quản lý lịch hẹn.
-4: Tìm lịch hẹn đang ở trạng thái Chờ xác nhận.
-5: Thực hiện Hủy lịch hẹn.
-6: Đăng xuất Admin.
-7: Đăng nhập lại bằng Patient sở hữu lịch hẹn.
-8: Mở trang Lịch hẹn của tôi.
-9: Kiểm tra lịch hẹn vừa được Admin hủy.</t>
+    <t>1: Patient thực hiện đặt một lịch khám hợp lệ và ghi nhận thông tin lịch vừa tạo.
+2: Đăng nhập bằng tài khoản Admin và mở trang Quản lý lịch hẹn.
+3: Tìm đúng lịch hẹn vừa tạo đang ở trạng thái “Chờ xác nhận”.
+4: Admin thực hiện Hủy lịch hẹn.
+5: Kiểm tra lịch hẹn được cập nhật thành “Đã hủy” trên trang Admin.
+6: Đăng nhập lại bằng Patient sở hữu lịch hẹn.
+7: Mở trang Lịch hẹn của tôi và tìm lịch vừa bị hủy.
+8: Kiểm tra lịch vẫn tồn tại, thông tin không thay đổi và trạng thái là “Đã hủy”.</t>
   </si>
   <si>
     <t>Lịch hẹn vẫn tồn tại trong lịch sử danh sách.
@@ -175,15 +177,15 @@
     <t>Kiểm tra lịch hẹn được cập nhật đúng xuyên suốt từ khi Patient đặt lịch, Admin xác nhận đến khi Doctor hoàn thành khám.</t>
   </si>
   <si>
-    <t>1: Patient thực hiện đặt một lịch khám hợp lệ với Doctor.
-2: Mở Lịch hẹn của tôi và kiểm tra lịch vừa tạo.
-3: Đăng nhập Admin và xác nhận lịch hẹn.
-4: Đăng nhập Doctor được Patient đặt lịch.
-5: Mở Lịch hẹn bệnh nhân và tìm lịch vừa được xác nhận.
-6: Chọn Khám bệnh, nhập kết quả khám và lưu hồ sơ bệnh án.
-7: Đăng xuất Doctor và đăng nhập lại bằng Patient.
-8: Mở Lịch hẹn của tôi.
-9: Kiểm tra trạng thái và thông tin lịch hẹn sau khi hoàn thành khám.</t>
+    <t>1: Patient thực hiện đặt một lịch khám hợp lệ với Doctor và ghi nhận thông tin lịch.
+2: Mở Lịch hẹn của tôi và kiểm tra lịch vừa tạo có trạng thái “Chờ xác nhận”.
+3: Đăng nhập Admin, tìm đúng lịch hẹn và thực hiện Xác nhận.
+4: Kiểm tra lịch được cập nhật thành “Đã xác nhận”.
+5: Đăng nhập bằng Doctor của lịch hẹn và mở Lịch hẹn bệnh nhân.
+6: Tìm đúng lịch đã được Admin xác nhận và thực hiện Khám bệnh.
+7: Nhập kết quả khám và lưu hồ sơ bệnh án thành công.
+8: Đăng nhập lại bằng Patient và mở Lịch hẹn của tôi.
+9: Kiểm tra đúng lịch hẹn chuyển thành “Đã hoàn thành” và các thông tin ban đầu không bị thay đổi.</t>
   </si>
   <si>
     <t>Sau khi Patient đặt lịch, lịch được tạo với trạng thái “Chờ xác nhận”.
@@ -209,13 +211,15 @@
     <t>Kiểm tra khung giờ của một lịch hẹn đã bị hủy có thể được sử dụng để tạo lịch hẹn mới.</t>
   </si>
   <si>
-    <t>1: Patient A đặt lịch với Doctor tại một ngày giờ hợp lệ.
-2: Admin hủy lịch hẹn của Patient A.
-3: Đăng nhập bằng Patient B.
-4: Mở chức năng đặt lịch với cùng Doctor.
-5: Chọn đúng ngày và giờ của lịch đã bị hủy.
-6: Nhập ghi chú và thực hiện đặt lịch.
-7: Mở Lịch hẹn của tôi và kiểm tra lịch mới.</t>
+    <t>1: Patient A thực hiện đặt lịch với Doctor tại một ngày và khung giờ hợp lệ.
+2: Ghi nhận Doctor, ngày và khung giờ của lịch vừa tạo.
+3: Đăng nhập Admin, tìm đúng lịch của Patient A và thực hiện Hủy lịch.
+4: Kiểm tra lịch của Patient A được cập nhật thành “Đã hủy”.
+5: Đăng nhập bằng Patient B và mở chức năng đặt lịch với cùng Doctor.
+6: Chọn lại đúng ngày và khung giờ của lịch vừa bị hủy.
+7: Nhập ghi chú và thực hiện đặt lịch mới.
+8: Mở Lịch hẹn của tôi và tìm lịch mới của Patient B.
+9: Kiểm tra lịch mới được tạo thành công với trạng thái “Chờ xác nhận” tại đúng khung giờ đã được giải phóng.</t>
   </si>
   <si>
     <t>Lịch của Patient A vẫn giữ trạng thái “Đã hủy”.
@@ -245,12 +249,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
@@ -457,30 +461,30 @@
   </cellStyleXfs>
   <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -498,30 +502,30 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -744,7 +748,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -767,9 +771,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -796,9 +800,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -827,11 +831,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -858,13 +862,13 @@
     </row>
     <row r="4" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -891,13 +895,13 @@
     </row>
     <row r="5" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -924,13 +928,13 @@
     </row>
     <row r="6" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -961,7 +965,7 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -1026,21 +1030,21 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="31" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="29" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="34" t="s">
@@ -1071,16 +1075,16 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1102,14 +1106,14 @@
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="37"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="24"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="27"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1132,15 +1136,15 @@
       <c r="A12" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="24"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="27"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1159,7 +1163,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>20</v>
       </c>
@@ -1172,8 +1176,8 @@
       <c r="D13" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
       <c r="G13" s="17" t="s">
         <v>24</v>
       </c>
@@ -1181,7 +1185,7 @@
         <v>46245</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>25</v>
@@ -1208,15 +1212,15 @@
       <c r="A14" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="24"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="27"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -1235,7 +1239,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="194.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>27</v>
       </c>
@@ -1248,8 +1252,8 @@
       <c r="D15" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
       <c r="G15" s="17" t="s">
         <v>31</v>
       </c>
@@ -1257,7 +1261,7 @@
         <v>46245</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>32</v>
@@ -1280,7 +1284,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="177" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>33</v>
       </c>
@@ -1293,8 +1297,8 @@
       <c r="D16" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
       <c r="G16" s="17" t="s">
         <v>37</v>
       </c>
@@ -1302,7 +1306,7 @@
         <v>46245</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>38</v>
@@ -1329,15 +1333,15 @@
       <c r="A17" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="24"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="27"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -1369,8 +1373,8 @@
       <c r="D18" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
       <c r="G18" s="17" t="s">
         <v>44</v>
       </c>
@@ -1378,7 +1382,7 @@
         <v>46245</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>45</v>
@@ -1405,15 +1409,15 @@
       <c r="A19" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="24"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="27"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -1432,7 +1436,7 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="177.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="230.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>47</v>
       </c>
@@ -1445,8 +1449,8 @@
       <c r="D20" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
       <c r="G20" s="17" t="s">
         <v>51</v>
       </c>
@@ -1454,7 +1458,7 @@
         <v>46245</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>52</v>
@@ -29392,11 +29396,11 @@
     <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
-    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
-    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0800-000002000000}"/>
-    <hyperlink ref="G18" r:id="rId4" xr:uid="{00000000-0004-0000-0800-000003000000}"/>
-    <hyperlink ref="G20" r:id="rId5" xr:uid="{00000000-0004-0000-0800-000004000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="G18" r:id="rId4" xr:uid="{00000000-0004-0000-0900-000003000000}"/>
+    <hyperlink ref="G20" r:id="rId5" xr:uid="{00000000-0004-0000-0900-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
